--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,12 +521,92 @@
         <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051584106881</v>
+        <v>0105158410688128101011610133100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105158410688128101011610133100</v>
+        <v>0105158410688128101011610133105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,95 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2</v>
+      </c>
+      <c r="C29" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105158410688128101011610133105</v>
+        <v>01051584106881281010116101331053310810615550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -692,10 +692,90 @@
       <c r="C31" t="str">
         <v>606_康乃馨橙光_orange_undefined_20stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051584106881281010116101331053310810615550</v>
+        <v>01051584106881281010116101331053310810615555510255151013150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -772,6 +772,9 @@
       <c r="A41" t="str">
         <v>3</v>
       </c>
+      <c r="C41" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -775,6 +775,9 @@
       <c r="C41" t="str">
         <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -833,7 +836,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051584106881281010116101331053310810615555510255151013150</v>
+        <v>010515841068812810101161013310533108106155555102551510131520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -779,9 +779,90 @@
         <v>20</v>
       </c>
     </row>
+    <row r="42" xml:space="preserve">
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>516_火焰兰_Crocosmia_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>102_绣球重瓣白_Hydrangea White D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F47" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F48" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -836,7 +917,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010515841068812810101161013310533108106155555102551510131520</v>
+        <v>0105158410688128101011610133105331081061555551025515101315201010101010203030151</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -857,12 +857,96 @@
         <v>574_迷你菊白_undefined_undefined_1bunch</v>
       </c>
       <c r="F51" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>4</v>
+      </c>
+      <c r="C52" t="str">
+        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>700_米酒果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>5</v>
+      </c>
+      <c r="C57" t="str">
+        <v>326_红继木_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>595_玉兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F60" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -917,7 +1001,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105158410688128101011610133105331081061555551025515101315201010101010203030151</v>
+        <v>0105158410688128101011610133105331081061555551025515101315201010101010203030151551051510155540</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -943,10 +943,37 @@
       <c r="C61" t="str">
         <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F63" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L64"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1001,7 +1028,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105158410688128101011610133105331081061555551025515101315201010101010203030151551051510155540</v>
+        <v>010515841068812810101161013310533108106155555102551510131520101010101020303015155105151015554105155</v>
       </c>
     </row>
   </sheetData>
